--- a/planilhas_gets/03.Atividades/19.horasTrabalhadas_julho2026.xlsx
+++ b/planilhas_gets/03.Atividades/19.horasTrabalhadas_julho2026.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="horasTrabalhadas20260702083235" r:id="rId3" sheetId="1"/>
+    <sheet name="horasTrabalhadas20260702091700" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
